--- a/data/input/list2_names_test.xlsx
+++ b/data/input/list2_names_test.xlsx
@@ -10,7 +10,7 @@
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="8_{4F291360-40D1-0F42-94C6-393DD0FE6C32}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6380" yWindow="3380" windowWidth="26840" windowHeight="15680" xr2:uid="{91570E31-31D8-1F47-93D4-5DC953FB94AE}"/>
+    <workbookView xWindow="10880" yWindow="2680" windowWidth="26840" windowHeight="15680" xr2:uid="{91570E31-31D8-1F47-93D4-5DC953FB94AE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -789,4 +789,10 @@
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
+</file>
+
+<file path=docMetadata/LabelInfo.xml><?xml version="1.0" encoding="utf-8"?>
+<clbl:labelList xmlns:clbl="http://schemas.microsoft.com/office/2020/mipLabelMetadata">
+  <clbl:label id="{6b902693-1074-40aa-9e21-d89446a2ebb5}" enabled="0" method="" siteId="{6b902693-1074-40aa-9e21-d89446a2ebb5}" removed="1"/>
+</clbl:labelList>
 </file>